--- a/qms/CCO-Domains-IRI-Registry.xlsx
+++ b/qms/CCO-Domains-IRI-Registry.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4a83c217d0612bbe/CCO-Domains/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:9_{5602A169-9B5C-C942-9CBD-A4824E1F6C2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8A37B82-1881-F140-BAC6-D468A8DE6089}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="13_ncr:9_{5602A169-9B5C-C942-9CBD-A4824E1F6C2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF990DA0-5B4F-B240-A71A-CF0AFF509735}"/>
   <bookViews>
-    <workbookView xWindow="11980" yWindow="5980" windowWidth="27640" windowHeight="16680" xr2:uid="{A52E4F06-8FCF-0847-8AC9-44ACCAF759E2}"/>
+    <workbookView xWindow="5000" yWindow="3840" windowWidth="27640" windowHeight="16680" xr2:uid="{A52E4F06-8FCF-0847-8AC9-44ACCAF759E2}"/>
   </bookViews>
   <sheets>
     <sheet name="CCO-Domains-IRI-Registry" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="43">
   <si>
     <t>ent ID</t>
   </si>
@@ -121,22 +121,34 @@
     <t>A non-Name Identifier for a person.</t>
   </si>
   <si>
+    <t>ent00000001</t>
+  </si>
+  <si>
+    <t>https://purl.org/cco/ent00000001</t>
+  </si>
+  <si>
     <t>Full Name</t>
   </si>
   <si>
-    <t>https://purl.org/cco/ent00000003</t>
-  </si>
-  <si>
     <t xml:space="preserve">A Designative Name comprising all or most of a person's various names, e.g. Given Name, Alternate Name, Family Name, etc. but may include initials for some names, as presented by the individual, who may give different versions at different times.  </t>
   </si>
   <si>
     <t xml:space="preserve">A Calendar Date Identifier designating when a Person was born. </t>
   </si>
   <si>
-    <t>https://purl.org/cco/ont00000001</t>
-  </si>
-  <si>
-    <t>ont00000001</t>
+    <t>https://purl.org/cco/ont00000003</t>
+  </si>
+  <si>
+    <t>ent00000002</t>
+  </si>
+  <si>
+    <t>https://purl.org/cco/ent00000002</t>
+  </si>
+  <si>
+    <t>Given Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A designative Name assigned to a person, usually at birth.   </t>
   </si>
 </sst>
 </file>
@@ -1029,7 +1041,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35BA39B8-40D1-AE49-86C6-FEA221B28AD5}">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.83203125" bestFit="1" customWidth="1"/>
@@ -1073,13 +1085,13 @@
     </row>
     <row r="2" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D2" t="s">
         <v>13</v>
@@ -1088,10 +1100,10 @@
         <v>14</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H2" t="s">
         <v>17</v>
@@ -1100,15 +1112,15 @@
         <v>46135</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" t="s">
-        <v>12</v>
+    <row r="3" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="D3" t="s">
         <v>13</v>
@@ -1116,28 +1128,28 @@
       <c r="E3" t="s">
         <v>14</v>
       </c>
-      <c r="F3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" t="s">
-        <v>16</v>
+      <c r="F3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="H3" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="6">
-        <v>46133</v>
+      <c r="I3" s="5">
+        <v>46135</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D4" t="s">
         <v>13</v>
@@ -1146,76 +1158,105 @@
         <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G4" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="H4" t="s">
         <v>17</v>
       </c>
       <c r="I4" s="6">
-        <v>46098</v>
-      </c>
-      <c r="J4" t="s">
-        <v>22</v>
+        <v>46133</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E5" t="s">
         <v>14</v>
       </c>
       <c r="F5" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="G5" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="H5" t="s">
         <v>17</v>
       </c>
       <c r="I5" s="6">
-        <v>46130</v>
+        <v>46098</v>
+      </c>
+      <c r="J5" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E6" t="s">
         <v>14</v>
       </c>
       <c r="F6" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G6" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H6" t="s">
         <v>17</v>
       </c>
       <c r="I6" s="6">
+        <v>46130</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7" s="6">
         <v>46133</v>
       </c>
     </row>
@@ -1223,6 +1264,8 @@
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{B2333AC5-E038-374C-A8CF-151443BCFC0C}"/>
     <hyperlink ref="F2" r:id="rId2" xr:uid="{168D9468-2691-9544-B6A3-C1C5A905B026}"/>
+    <hyperlink ref="F3" r:id="rId3" xr:uid="{795A554E-5B47-5D49-9E30-AFE500713F1A}"/>
+    <hyperlink ref="B3" r:id="rId4" xr:uid="{0E826CB8-7D54-464F-B130-80C648A97858}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/qms/CCO-Domains-IRI-Registry.xlsx
+++ b/qms/CCO-Domains-IRI-Registry.xlsx
@@ -1,26 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4a83c217d0612bbe/CCO-Domains/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/39832cccfcb40ceb/Desktop/CCO=domins/qms/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="32" documentId="13_ncr:9_{5602A169-9B5C-C942-9CBD-A4824E1F6C2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF990DA0-5B4F-B240-A71A-CF0AFF509735}"/>
+  <xr:revisionPtr revIDLastSave="92" documentId="13_ncr:9_{5602A169-9B5C-C942-9CBD-A4824E1F6C2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{922BAA1E-69A3-4A01-BC17-31ECED614A1A}"/>
   <bookViews>
-    <workbookView xWindow="5000" yWindow="3840" windowWidth="27640" windowHeight="16680" xr2:uid="{A52E4F06-8FCF-0847-8AC9-44ACCAF759E2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{A52E4F06-8FCF-0847-8AC9-44ACCAF759E2}"/>
   </bookViews>
   <sheets>
     <sheet name="CCO-Domains-IRI-Registry" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="67">
   <si>
     <t>ent ID</t>
   </si>
@@ -149,6 +162,78 @@
   </si>
   <si>
     <t xml:space="preserve">A designative Name assigned to a person, usually at birth.   </t>
+  </si>
+  <si>
+    <t>Family Name</t>
+  </si>
+  <si>
+    <t>A designative name often referred to as a "last name" in Western contexts or a "surname" in formal contexts.</t>
+  </si>
+  <si>
+    <t>ent00000004</t>
+  </si>
+  <si>
+    <t>https://purl.org/cco/ent00000004</t>
+  </si>
+  <si>
+    <t>A designative name that is used as a secondary name instead of primary or legal name.</t>
+  </si>
+  <si>
+    <t>Alternate Name</t>
+  </si>
+  <si>
+    <t>ent00000006</t>
+  </si>
+  <si>
+    <t>https://purl.org/cco/ent00000006</t>
+  </si>
+  <si>
+    <t>https://purl.org/cco/ent00000003</t>
+  </si>
+  <si>
+    <t>ent00000003</t>
+  </si>
+  <si>
+    <t>Additional Name</t>
+  </si>
+  <si>
+    <t>A designative name that refers as an extra identifier and supplements a primary name.</t>
+  </si>
+  <si>
+    <t>Suffix</t>
+  </si>
+  <si>
+    <t>https://purl.org/cco/ent00000005</t>
+  </si>
+  <si>
+    <t>A designative name added after the person's full name to add more information (professional, generational or academic).</t>
+  </si>
+  <si>
+    <t>ent00000005</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>https://purl.org/cco/ent00000057</t>
+  </si>
+  <si>
+    <t>ent00000057</t>
+  </si>
+  <si>
+    <t>A designative name added before the person's given name to add more information (professional, marital status or religious).</t>
+  </si>
+  <si>
+    <t>ent00000058</t>
+  </si>
+  <si>
+    <t>Surname2</t>
+  </si>
+  <si>
+    <t>A designative name that represents the second family name, commonly a maternal surname.</t>
+  </si>
+  <si>
+    <t>https://purl.org/cco/ent00000058</t>
   </si>
 </sst>
 </file>
@@ -156,7 +241,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
   <fonts count="21" x14ac:knownFonts="1">
     <font>
@@ -662,9 +747,9 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="42"/>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -722,6 +807,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1041,17 +1130,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35BA39B8-40D1-AE49-86C6-FEA221B28AD5}">
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:J13"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="28.83203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.83203125" style="6"/>
+    <col min="1" max="1" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" ht="22" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1083,7 +1172,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>33</v>
       </c>
@@ -1112,7 +1201,7 @@
         <v>46135</v>
       </c>
     </row>
-    <row r="3" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>39</v>
       </c>
@@ -1141,7 +1230,7 @@
         <v>46135</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -1170,7 +1259,7 @@
         <v>46133</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -1202,7 +1291,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -1231,7 +1320,7 @@
         <v>46130</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>29</v>
       </c>
@@ -1258,6 +1347,180 @@
       </c>
       <c r="I7" s="6">
         <v>46133</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" t="s">
+        <v>38</v>
+      </c>
+      <c r="G8" t="s">
+        <v>44</v>
+      </c>
+      <c r="H8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I8" s="6">
+        <v>46140</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9" s="6">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" t="s">
+        <v>38</v>
+      </c>
+      <c r="G10" t="s">
+        <v>54</v>
+      </c>
+      <c r="H10" t="s">
+        <v>17</v>
+      </c>
+      <c r="I10" s="6">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" t="s">
+        <v>38</v>
+      </c>
+      <c r="G11" t="s">
+        <v>57</v>
+      </c>
+      <c r="H11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I11" s="6">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" t="s">
+        <v>38</v>
+      </c>
+      <c r="G12" t="s">
+        <v>62</v>
+      </c>
+      <c r="H12" t="s">
+        <v>17</v>
+      </c>
+      <c r="I12" s="6">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" t="s">
+        <v>64</v>
+      </c>
+      <c r="D13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" t="s">
+        <v>38</v>
+      </c>
+      <c r="G13" t="s">
+        <v>65</v>
+      </c>
+      <c r="H13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I13" s="6">
+        <v>46143</v>
       </c>
     </row>
   </sheetData>
@@ -1266,6 +1529,12 @@
     <hyperlink ref="F2" r:id="rId2" xr:uid="{168D9468-2691-9544-B6A3-C1C5A905B026}"/>
     <hyperlink ref="F3" r:id="rId3" xr:uid="{795A554E-5B47-5D49-9E30-AFE500713F1A}"/>
     <hyperlink ref="B3" r:id="rId4" xr:uid="{0E826CB8-7D54-464F-B130-80C648A97858}"/>
+    <hyperlink ref="B8" r:id="rId5" xr:uid="{E6C16A15-B013-45F3-8BBF-5330BC016B73}"/>
+    <hyperlink ref="B9" r:id="rId6" xr:uid="{BB499331-F7C3-4525-AF74-B3F65714E291}"/>
+    <hyperlink ref="B10" r:id="rId7" xr:uid="{DCF4676A-C50C-491F-ADD8-BC821EFE7F58}"/>
+    <hyperlink ref="B11" r:id="rId8" xr:uid="{8C6EA946-86EF-4DB4-A30F-8C66C2B0853C}"/>
+    <hyperlink ref="B12" r:id="rId9" xr:uid="{C8C40842-DFC8-4435-A506-F8F46A315A0E}"/>
+    <hyperlink ref="B13" r:id="rId10" xr:uid="{6626F466-0911-48C0-8ABB-373DC453D63F}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/qms/CCO-Domains-IRI-Registry.xlsx
+++ b/qms/CCO-Domains-IRI-Registry.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/39832cccfcb40ceb/Desktop/CCO=domins/qms/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="92" documentId="13_ncr:9_{5602A169-9B5C-C942-9CBD-A4824E1F6C2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{922BAA1E-69A3-4A01-BC17-31ECED614A1A}"/>
+  <xr:revisionPtr revIDLastSave="105" documentId="13_ncr:9_{5602A169-9B5C-C942-9CBD-A4824E1F6C2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0E14C77-9D88-4512-A280-E8AC35893148}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{A52E4F06-8FCF-0847-8AC9-44ACCAF759E2}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="77">
   <si>
     <t>ent ID</t>
   </si>
@@ -234,6 +234,36 @@
   </si>
   <si>
     <t>https://purl.org/cco/ent00000058</t>
+  </si>
+  <si>
+    <t>ent00000023</t>
+  </si>
+  <si>
+    <t>https://purl.org/cco/ent00000023</t>
+  </si>
+  <si>
+    <t>Telephone Number</t>
+  </si>
+  <si>
+    <t>StagingOntology</t>
+  </si>
+  <si>
+    <t>https://purl.org/cco/ont00000958</t>
+  </si>
+  <si>
+    <t>An Information Content Entity (ICE) that consists of a unique sequence of digits assigned to a paticular telecommunication endpoint, enabling that person to be contacted through a telephone network.</t>
+  </si>
+  <si>
+    <t>ent00000024</t>
+  </si>
+  <si>
+    <t>https://purl.org/cco/ent00000024</t>
+  </si>
+  <si>
+    <t>Email Address</t>
+  </si>
+  <si>
+    <t>An Information Content Entity (ICE) that consistes of a unique address assigned to a person, enabling the sending and receiving of electronic messages through a mail server over the network.</t>
   </si>
 </sst>
 </file>
@@ -1130,7 +1160,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35BA39B8-40D1-AE49-86C6-FEA221B28AD5}">
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.875" bestFit="1" customWidth="1"/>
@@ -1521,6 +1551,64 @@
       </c>
       <c r="I13" s="6">
         <v>46143</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C14" t="s">
+        <v>69</v>
+      </c>
+      <c r="D14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" t="s">
+        <v>70</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G14" t="s">
+        <v>72</v>
+      </c>
+      <c r="H14" t="s">
+        <v>17</v>
+      </c>
+      <c r="I14" s="6">
+        <v>46147</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C15" t="s">
+        <v>75</v>
+      </c>
+      <c r="D15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" t="s">
+        <v>70</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G15" t="s">
+        <v>76</v>
+      </c>
+      <c r="H15" t="s">
+        <v>17</v>
+      </c>
+      <c r="I15" s="6">
+        <v>46147</v>
       </c>
     </row>
   </sheetData>
@@ -1535,6 +1623,10 @@
     <hyperlink ref="B11" r:id="rId8" xr:uid="{8C6EA946-86EF-4DB4-A30F-8C66C2B0853C}"/>
     <hyperlink ref="B12" r:id="rId9" xr:uid="{C8C40842-DFC8-4435-A506-F8F46A315A0E}"/>
     <hyperlink ref="B13" r:id="rId10" xr:uid="{6626F466-0911-48C0-8ABB-373DC453D63F}"/>
+    <hyperlink ref="B14" r:id="rId11" xr:uid="{480AB35C-38AD-4FA8-B504-33F90504CCD0}"/>
+    <hyperlink ref="F14" r:id="rId12" xr:uid="{027A5B4A-2E08-465E-993F-67929EC47746}"/>
+    <hyperlink ref="B15" r:id="rId13" xr:uid="{B9F3210E-622A-42BD-9FF2-D6DCF77E03DE}"/>
+    <hyperlink ref="F15" r:id="rId14" xr:uid="{48E6F3B8-1518-4114-8E93-22D0546AC636}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/qms/CCO-Domains-IRI-Registry.xlsx
+++ b/qms/CCO-Domains-IRI-Registry.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/39832cccfcb40ceb/Desktop/CCO=domins/qms/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="105" documentId="13_ncr:9_{5602A169-9B5C-C942-9CBD-A4824E1F6C2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0E14C77-9D88-4512-A280-E8AC35893148}"/>
+  <xr:revisionPtr revIDLastSave="107" documentId="13_ncr:9_{5602A169-9B5C-C942-9CBD-A4824E1F6C2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7286C7E6-F3DE-415E-834E-DE76E4A728D5}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{A52E4F06-8FCF-0847-8AC9-44ACCAF759E2}"/>
   </bookViews>
@@ -251,9 +251,6 @@
     <t>https://purl.org/cco/ont00000958</t>
   </si>
   <si>
-    <t>An Information Content Entity (ICE) that consists of a unique sequence of digits assigned to a paticular telecommunication endpoint, enabling that person to be contacted through a telephone network.</t>
-  </si>
-  <si>
     <t>ent00000024</t>
   </si>
   <si>
@@ -263,7 +260,10 @@
     <t>Email Address</t>
   </si>
   <si>
-    <t>An Information Content Entity (ICE) that consistes of a unique address assigned to a person, enabling the sending and receiving of electronic messages through a mail server over the network.</t>
+    <t>An Information Content Entity (ICE) that consists of a unique address assigned to a person, enabling the sending and receiving of electronic messages through a mail server over the network.</t>
+  </si>
+  <si>
+    <t>An Information Content Entity (ICE) that consists of a unique sequence of digits assigned to a particular telecommunication endpoint, enabling that person to be contacted through a telephone network.</t>
   </si>
 </sst>
 </file>
@@ -1573,7 +1573,7 @@
         <v>71</v>
       </c>
       <c r="G14" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H14" t="s">
         <v>17</v>
@@ -1584,13 +1584,13 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>72</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="C15" t="s">
         <v>74</v>
-      </c>
-      <c r="C15" t="s">
-        <v>75</v>
       </c>
       <c r="D15" t="s">
         <v>13</v>
@@ -1602,7 +1602,7 @@
         <v>71</v>
       </c>
       <c r="G15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H15" t="s">
         <v>17</v>
